--- a/Assets/StreamingAssets/Dialog.xlsx
+++ b/Assets/StreamingAssets/Dialog.xlsx
@@ -99,7 +99,7 @@
     <t>CharacterImageName</t>
   </si>
   <si>
-    <t>Alv/Mask1</t>
+    <t>Alv/Mask</t>
   </si>
   <si>
     <t>……？</t>
